--- a/Output/Models/Exposure_models_malf_card_bin_div10_Masculino.xlsx
+++ b/Output/Models/Exposure_models_malf_card_bin_div10_Masculino.xlsx
@@ -501,22 +501,22 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.9088464683439254</v>
+        <v>0.9014713503238301</v>
       </c>
       <c r="C3">
-        <v>0.05986501760449519</v>
+        <v>0.06110774318882124</v>
       </c>
       <c r="D3">
-        <v>-1.596576842480292</v>
+        <v>-1.697444733478221</v>
       </c>
       <c r="E3">
-        <v>0.1103600643243745</v>
+        <v>0.08961261136403385</v>
       </c>
       <c r="F3">
-        <v>0.8082269515894044</v>
+        <v>0.7997180965897236</v>
       </c>
       <c r="G3">
-        <v>1.021992524991732</v>
+        <v>1.016171322019715</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -564,22 +564,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.9579763343336334</v>
+        <v>0.9993700629472999</v>
       </c>
       <c r="C4">
-        <v>0.05777478081340849</v>
+        <v>0.05896300340849019</v>
       </c>
       <c r="D4">
-        <v>-0.7430959306598021</v>
+        <v>-0.0106869648759777</v>
       </c>
       <c r="E4">
-        <v>0.4574236031740558</v>
+        <v>0.9914731980333306</v>
       </c>
       <c r="F4">
-        <v>0.8554148747339441</v>
+        <v>0.8903011536115572</v>
       </c>
       <c r="G4">
-        <v>1.072834579161064</v>
+        <v>1.121800773439237</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -627,22 +627,22 @@
         </is>
       </c>
       <c r="B5">
-        <v>1.141838757278795</v>
+        <v>1.145735110003088</v>
       </c>
       <c r="C5">
-        <v>0.05694125408014267</v>
+        <v>0.0571854175595319</v>
       </c>
       <c r="D5">
-        <v>2.329416696766322</v>
+        <v>2.379040921218629</v>
       </c>
       <c r="E5">
-        <v>0.01983700138496678</v>
+        <v>0.01735774892096064</v>
       </c>
       <c r="F5">
-        <v>1.021259940452041</v>
+        <v>1.024254560143933</v>
       </c>
       <c r="G5">
-        <v>1.276654156283543</v>
+        <v>1.281623722631336</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="O5">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="6">
@@ -879,22 +879,22 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.5216416475813548</v>
+        <v>0.4960087390937506</v>
       </c>
       <c r="C9">
-        <v>0.3748597006636166</v>
+        <v>0.3828582140758549</v>
       </c>
       <c r="D9">
-        <v>-1.736047978969151</v>
+        <v>-1.831387462756327</v>
       </c>
       <c r="E9">
-        <v>0.08255535141343721</v>
+        <v>0.06704273126398977</v>
       </c>
       <c r="F9">
-        <v>0.2502021874228738</v>
+        <v>0.2342069754634483</v>
       </c>
       <c r="G9">
-        <v>1.087560469771151</v>
+        <v>1.05045833400367</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -942,22 +942,22 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.7070620128487183</v>
+        <v>0.9231362957720682</v>
       </c>
       <c r="C10">
-        <v>0.363549997248326</v>
+        <v>0.3719789635221135</v>
       </c>
       <c r="D10">
-        <v>-0.9534779449826565</v>
+        <v>-0.2150078288432857</v>
       </c>
       <c r="E10">
-        <v>0.3403479655845482</v>
+        <v>0.8297612147684695</v>
       </c>
       <c r="F10">
-        <v>0.3467393945797482</v>
+        <v>0.4452836603824717</v>
       </c>
       <c r="G10">
-        <v>1.441822584421391</v>
+        <v>1.913792704272606</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1005,22 +1005,22 @@
         </is>
       </c>
       <c r="B11">
-        <v>2.068082763824187</v>
+        <v>2.08339977080319</v>
       </c>
       <c r="C11">
-        <v>0.3588947625182643</v>
+        <v>0.3596144002085212</v>
       </c>
       <c r="D11">
-        <v>2.024610144596239</v>
+        <v>2.041078066205494</v>
       </c>
       <c r="E11">
-        <v>0.04290741174984262</v>
+        <v>0.0412430681563066</v>
       </c>
       <c r="F11">
-        <v>1.023472409004108</v>
+        <v>1.029599397196972</v>
       </c>
       <c r="G11">
-        <v>4.178877984789447</v>
+        <v>4.215770344077226</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="O11">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="12">
@@ -1257,22 +1257,22 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.5417423009542014</v>
+        <v>0.513260288721941</v>
       </c>
       <c r="C15">
-        <v>0.3525730612302579</v>
+        <v>0.3605808569525368</v>
       </c>
       <c r="D15">
-        <v>-1.73854703466121</v>
+        <v>-1.849715990754145</v>
       </c>
       <c r="E15">
-        <v>0.08211446993838785</v>
+        <v>0.06435449452754576</v>
       </c>
       <c r="F15">
-        <v>0.2714451048769062</v>
+        <v>0.2531690908523775</v>
       </c>
       <c r="G15">
-        <v>1.081193638677849</v>
+        <v>1.040554054572718</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1320,22 +1320,22 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.7260495644203621</v>
+        <v>0.9494801295833923</v>
       </c>
       <c r="C16">
-        <v>0.3394032446797374</v>
+        <v>0.344910790447081</v>
       </c>
       <c r="D16">
-        <v>-0.9432349305861499</v>
+        <v>-0.1503016943132554</v>
       </c>
       <c r="E16">
-        <v>0.3455607502195968</v>
+        <v>0.8805265963071753</v>
       </c>
       <c r="F16">
-        <v>0.3733066303585448</v>
+        <v>0.4829445653991498</v>
       </c>
       <c r="G16">
-        <v>1.412104492997338</v>
+        <v>1.866699785157749</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1383,22 +1383,22 @@
         </is>
       </c>
       <c r="B17">
-        <v>2.092762367513013</v>
+        <v>2.064751828283572</v>
       </c>
       <c r="C17">
-        <v>0.3297969384519823</v>
+        <v>0.3312304636586827</v>
       </c>
       <c r="D17">
-        <v>2.239210902627939</v>
+        <v>2.188838644774936</v>
       </c>
       <c r="E17">
-        <v>0.02514219678918331</v>
+        <v>0.02860856982370596</v>
       </c>
       <c r="F17">
-        <v>1.096468738991298</v>
+        <v>1.078757871035127</v>
       </c>
       <c r="G17">
-        <v>3.994326669912865</v>
+        <v>3.951952729030456</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         </is>
       </c>
       <c r="O17">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="18">
@@ -1635,22 +1635,22 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.9532828075212826</v>
+        <v>0.9490800315159675</v>
       </c>
       <c r="C21">
-        <v>0.03475527610342542</v>
+        <v>0.03547545918342759</v>
       </c>
       <c r="D21">
-        <v>-1.376587088591275</v>
+        <v>-1.47319168402378</v>
       </c>
       <c r="E21">
-        <v>0.1686399449949737</v>
+        <v>0.1406993567909515</v>
       </c>
       <c r="F21">
-        <v>0.8905083907513464</v>
+        <v>0.8853318134505306</v>
       </c>
       <c r="G21">
-        <v>1.020482367773001</v>
+        <v>1.017418432883053</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1698,22 +1698,22 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.978000131692514</v>
+        <v>1.001867076398143</v>
       </c>
       <c r="C22">
-        <v>0.03292034359449389</v>
+        <v>0.03279549828264064</v>
       </c>
       <c r="D22">
-        <v>-0.6757363946871802</v>
+        <v>0.05687779345268522</v>
       </c>
       <c r="E22">
-        <v>0.4992080243902923</v>
+        <v>0.9546425439278405</v>
       </c>
       <c r="F22">
-        <v>0.9168896407664322</v>
+        <v>0.9394951148166609</v>
       </c>
       <c r="G22">
-        <v>1.043183623266858</v>
+        <v>1.068379838213888</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1761,22 +1761,22 @@
         </is>
       </c>
       <c r="B23">
-        <v>1.070488702806036</v>
+        <v>1.07190782232287</v>
       </c>
       <c r="C23">
-        <v>0.02937138755372765</v>
+        <v>0.02966507231565096</v>
       </c>
       <c r="D23">
-        <v>2.319103095606694</v>
+        <v>2.340802394599168</v>
       </c>
       <c r="E23">
-        <v>0.02038944696431609</v>
+        <v>0.01924234860407498</v>
       </c>
       <c r="F23">
-        <v>1.010604244671579</v>
+        <v>1.011361657856177</v>
       </c>
       <c r="G23">
-        <v>1.133921679903247</v>
+        <v>1.136078642720655</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="O23">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="24">
@@ -2013,22 +2013,22 @@
         </is>
       </c>
       <c r="B27">
-        <v>0.5762744846467945</v>
+        <v>0.5503991997630947</v>
       </c>
       <c r="C27">
-        <v>0.3516749973151782</v>
+        <v>0.3592314610801869</v>
       </c>
       <c r="D27">
-        <v>-1.567274330436101</v>
+        <v>-1.662191402967264</v>
       </c>
       <c r="E27">
-        <v>0.1170505827560306</v>
+        <v>0.09647440322880163</v>
       </c>
       <c r="F27">
-        <v>0.2892564757896646</v>
+        <v>0.2722070818245373</v>
       </c>
       <c r="G27">
-        <v>1.148089358235881</v>
+        <v>1.112900065161154</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -2076,22 +2076,22 @@
         </is>
       </c>
       <c r="B28">
-        <v>0.7681315376921288</v>
+        <v>0.9958971401009168</v>
       </c>
       <c r="C28">
-        <v>0.3394243663289851</v>
+        <v>0.3454791611519717</v>
       </c>
       <c r="D28">
-        <v>-0.7771813506391282</v>
+        <v>-0.01190028280692808</v>
       </c>
       <c r="E28">
-        <v>0.4370517834646878</v>
+        <v>0.9905051721841058</v>
       </c>
       <c r="F28">
-        <v>0.3949272054977754</v>
+        <v>0.5059901820285319</v>
       </c>
       <c r="G28">
-        <v>1.49401219005308</v>
+        <v>1.960139047925753</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -2139,22 +2139,22 @@
         </is>
       </c>
       <c r="B29">
-        <v>2.03271533389041</v>
+        <v>2.045435355807483</v>
       </c>
       <c r="C29">
-        <v>0.330346639931743</v>
+        <v>0.3322437484484259</v>
       </c>
       <c r="D29">
-        <v>2.147358006450816</v>
+        <v>2.153872444868139</v>
       </c>
       <c r="E29">
-        <v>0.0317647911114628</v>
+        <v>0.03125017643453058</v>
       </c>
       <c r="F29">
-        <v>1.06386125766061</v>
+        <v>1.066545449637673</v>
       </c>
       <c r="G29">
-        <v>3.883900836580102</v>
+        <v>3.922763719266356</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="O29">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="30">
@@ -2391,22 +2391,22 @@
         </is>
       </c>
       <c r="B33">
-        <v>0.6888628185345836</v>
+        <v>0.6641237390903753</v>
       </c>
       <c r="C33">
-        <v>0.2421067256139489</v>
+        <v>0.2478052632683116</v>
       </c>
       <c r="D33">
-        <v>-1.539457977133145</v>
+        <v>-1.651646891666448</v>
       </c>
       <c r="E33">
-        <v>0.1236925293981822</v>
+        <v>0.09860655495855553</v>
       </c>
       <c r="F33">
-        <v>0.4285989727586473</v>
+        <v>0.4086173301548712</v>
       </c>
       <c r="G33">
-        <v>1.107170135535134</v>
+        <v>1.07939705018437</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2454,22 +2454,22 @@
         </is>
       </c>
       <c r="B34">
-        <v>0.8113408423717755</v>
+        <v>0.9802820255169817</v>
       </c>
       <c r="C34">
-        <v>0.2311223181595485</v>
+        <v>0.230315727382142</v>
       </c>
       <c r="D34">
-        <v>-0.9045731309181448</v>
+        <v>-0.08646811837451496</v>
       </c>
       <c r="E34">
-        <v>0.3656915752226096</v>
+        <v>0.9310942989762877</v>
       </c>
       <c r="F34">
-        <v>0.515788511691911</v>
+        <v>0.6241743776305593</v>
       </c>
       <c r="G34">
-        <v>1.276247817814407</v>
+        <v>1.539558309329468</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -2517,22 +2517,22 @@
         </is>
       </c>
       <c r="B35">
-        <v>1.644958041046858</v>
+        <v>1.636454982747344</v>
       </c>
       <c r="C35">
-        <v>0.206894218224758</v>
+        <v>0.209099687101535</v>
       </c>
       <c r="D35">
-        <v>2.405649037465814</v>
+        <v>2.355490403439192</v>
       </c>
       <c r="E35">
-        <v>0.01614376552498597</v>
+        <v>0.01849827483610626</v>
       </c>
       <c r="F35">
-        <v>1.096594710685173</v>
+        <v>1.086220729036118</v>
       </c>
       <c r="G35">
-        <v>2.467536028068228</v>
+        <v>2.465415029351334</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         </is>
       </c>
       <c r="O35">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="36">
@@ -2769,22 +2769,22 @@
         </is>
       </c>
       <c r="B39">
-        <v>0.9486735172314562</v>
+        <v>0.9351591771470044</v>
       </c>
       <c r="C39">
-        <v>0.1371888150761962</v>
+        <v>0.136847771734076</v>
       </c>
       <c r="D39">
-        <v>-0.3840733498669708</v>
+        <v>-0.4898766008074426</v>
       </c>
       <c r="E39">
-        <v>0.7009240832219796</v>
+        <v>0.6242212217962232</v>
       </c>
       <c r="F39">
-        <v>0.7250057418239398</v>
+        <v>0.7151555373368622</v>
       </c>
       <c r="G39">
-        <v>1.241343882370042</v>
+        <v>1.222842641838251</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2832,22 +2832,22 @@
         </is>
       </c>
       <c r="B40">
-        <v>0.9829668847624644</v>
+        <v>1.102958148064042</v>
       </c>
       <c r="C40">
-        <v>0.1382251763819723</v>
+        <v>0.1448670331261207</v>
       </c>
       <c r="D40">
-        <v>-0.124288843642586</v>
+        <v>0.6764533911215435</v>
       </c>
       <c r="E40">
-        <v>0.9010865802922416</v>
+        <v>0.4987528287290551</v>
       </c>
       <c r="F40">
-        <v>0.749689457547537</v>
+        <v>0.8303247649466592</v>
       </c>
       <c r="G40">
-        <v>1.288832178193404</v>
+        <v>1.465109470098742</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2895,22 +2895,22 @@
         </is>
       </c>
       <c r="B41">
-        <v>1.220887900016207</v>
+        <v>1.124025006588515</v>
       </c>
       <c r="C41">
-        <v>0.1309067628109384</v>
+        <v>0.1210753357447531</v>
       </c>
       <c r="D41">
-        <v>1.52458418992056</v>
+        <v>0.9656467054945735</v>
       </c>
       <c r="E41">
-        <v>0.1273628432640938</v>
+        <v>0.3342209959090819</v>
       </c>
       <c r="F41">
-        <v>0.944599586277751</v>
+        <v>0.8865770003640043</v>
       </c>
       <c r="G41">
-        <v>1.57798847899103</v>
+        <v>1.425067664644561</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="O41">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="42">
@@ -3147,22 +3147,22 @@
         </is>
       </c>
       <c r="B45">
-        <v>0.7203712603931336</v>
+        <v>0.6650213364675784</v>
       </c>
       <c r="C45">
-        <v>0.8644052458385932</v>
+        <v>0.8537290577035732</v>
       </c>
       <c r="D45">
-        <v>-0.3794384196676928</v>
+        <v>-0.477828592392813</v>
       </c>
       <c r="E45">
-        <v>0.7043623250503913</v>
+        <v>0.6327722088148802</v>
       </c>
       <c r="F45">
-        <v>0.1323650411065592</v>
+        <v>0.124778594076452</v>
       </c>
       <c r="G45">
-        <v>3.920481937391826</v>
+        <v>3.544304864391685</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -3210,22 +3210,22 @@
         </is>
       </c>
       <c r="B46">
-        <v>0.7136170489334422</v>
+        <v>1.616728754240337</v>
       </c>
       <c r="C46">
-        <v>0.8698167033755612</v>
+        <v>0.8898683738480989</v>
       </c>
       <c r="D46">
-        <v>-0.3879079411210688</v>
+        <v>0.5398605393190332</v>
       </c>
       <c r="E46">
-        <v>0.6980841612337145</v>
+        <v>0.5892932131592457</v>
       </c>
       <c r="F46">
-        <v>0.1297405984752171</v>
+        <v>0.2826049922400135</v>
       </c>
       <c r="G46">
-        <v>3.925134449150478</v>
+        <v>9.248993954670233</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -3273,22 +3273,22 @@
         </is>
       </c>
       <c r="B47">
-        <v>3.386528816675916</v>
+        <v>1.703564117518502</v>
       </c>
       <c r="C47">
-        <v>0.8443022750140214</v>
+        <v>0.7675288788528472</v>
       </c>
       <c r="D47">
-        <v>1.444749688606634</v>
+        <v>0.694074986341488</v>
       </c>
       <c r="E47">
-        <v>0.1485282074977423</v>
+        <v>0.4876351843326577</v>
       </c>
       <c r="F47">
-        <v>0.6472668663729754</v>
+        <v>0.3784745817644249</v>
       </c>
       <c r="G47">
-        <v>17.71846825783267</v>
+        <v>7.667967262073558</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="O47">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="48">
@@ -3525,22 +3525,22 @@
         </is>
       </c>
       <c r="B51">
-        <v>0.7512604782378458</v>
+        <v>0.6811024871515554</v>
       </c>
       <c r="C51">
-        <v>0.7873737666804371</v>
+        <v>0.7855938217430087</v>
       </c>
       <c r="D51">
-        <v>-0.363236441948288</v>
+        <v>-0.4888563000925151</v>
       </c>
       <c r="E51">
-        <v>0.7164282672590305</v>
+        <v>0.6249434358254521</v>
       </c>
       <c r="F51">
-        <v>0.1605376040741254</v>
+        <v>0.1460541134075082</v>
       </c>
       <c r="G51">
-        <v>3.515639276026311</v>
+        <v>3.176224121190597</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -3588,22 +3588,22 @@
         </is>
       </c>
       <c r="B52">
-        <v>0.7231950209269259</v>
+        <v>1.556898112675424</v>
       </c>
       <c r="C52">
-        <v>0.7868354308216678</v>
+        <v>0.8164631048440749</v>
       </c>
       <c r="D52">
-        <v>-0.411873108420771</v>
+        <v>0.5422112154901745</v>
       </c>
       <c r="E52">
-        <v>0.680432432186838</v>
+        <v>0.5876730099270254</v>
       </c>
       <c r="F52">
-        <v>0.1547034128007801</v>
+        <v>0.314257417579187</v>
       </c>
       <c r="G52">
-        <v>3.380733681467041</v>
+        <v>7.713204518526635</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="B53">
-        <v>3.247105409277432</v>
+        <v>1.797232689208659</v>
       </c>
       <c r="C53">
-        <v>0.7376813363704319</v>
+        <v>0.6877380631569141</v>
       </c>
       <c r="D53">
-        <v>1.596575510475666</v>
+        <v>0.8524293163633084</v>
       </c>
       <c r="E53">
-        <v>0.1103603614399563</v>
+        <v>0.3939758546142765</v>
       </c>
       <c r="F53">
-        <v>0.7648581438934369</v>
+        <v>0.4668749885727888</v>
       </c>
       <c r="G53">
-        <v>13.78516215475866</v>
+        <v>6.918437308098812</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         </is>
       </c>
       <c r="O53">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="54">
@@ -3903,22 +3903,22 @@
         </is>
       </c>
       <c r="B57">
-        <v>0.9964952875418028</v>
+        <v>0.9902793353683423</v>
       </c>
       <c r="C57">
-        <v>0.06236799012080146</v>
+        <v>0.06275278982069166</v>
       </c>
       <c r="D57">
-        <v>-0.05629279287981638</v>
+        <v>-0.1556619035181694</v>
       </c>
       <c r="E57">
-        <v>0.955108560181183</v>
+        <v>0.8762995276334332</v>
       </c>
       <c r="F57">
-        <v>0.8818353814209113</v>
+        <v>0.8756739796278709</v>
       </c>
       <c r="G57">
-        <v>1.126063751822912</v>
+        <v>1.119883866452566</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -3966,22 +3966,22 @@
         </is>
       </c>
       <c r="B58">
-        <v>0.9938787531495364</v>
+        <v>1.03210605466696</v>
       </c>
       <c r="C58">
-        <v>0.0603754596879295</v>
+        <v>0.05838420337853271</v>
       </c>
       <c r="D58">
-        <v>-0.1016979170031947</v>
+        <v>0.541266748551147</v>
       </c>
       <c r="E58">
-        <v>0.9189964555657558</v>
+        <v>0.5883237359782738</v>
       </c>
       <c r="F58">
-        <v>0.8829614078726697</v>
+        <v>0.920508073143006</v>
       </c>
       <c r="G58">
-        <v>1.118729501827248</v>
+        <v>1.157233639943</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -4029,22 +4029,22 @@
         </is>
       </c>
       <c r="B59">
-        <v>1.063836560733341</v>
+        <v>1.04397247976808</v>
       </c>
       <c r="C59">
-        <v>0.04896428059600425</v>
+        <v>0.04980105162813916</v>
       </c>
       <c r="D59">
-        <v>1.263814561021209</v>
+        <v>0.8641008037125247</v>
       </c>
       <c r="E59">
-        <v>0.206296593602401</v>
+        <v>0.3875325175435233</v>
       </c>
       <c r="F59">
-        <v>0.9664879426241403</v>
+        <v>0.9468873581616027</v>
       </c>
       <c r="G59">
-        <v>1.170990529773295</v>
+        <v>1.151011816895656</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         </is>
       </c>
       <c r="O59">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="60">
@@ -4281,22 +4281,22 @@
         </is>
       </c>
       <c r="B63">
-        <v>0.9981256050697142</v>
+        <v>0.9191457622460868</v>
       </c>
       <c r="C63">
-        <v>0.7498664035783648</v>
+        <v>0.7427159645336119</v>
       </c>
       <c r="D63">
-        <v>-0.002501984083751217</v>
+        <v>-0.1135165576127006</v>
       </c>
       <c r="E63">
-        <v>0.9980037076109738</v>
+        <v>0.9096210368516534</v>
       </c>
       <c r="F63">
-        <v>0.2295608144126299</v>
+        <v>0.21437957915363</v>
       </c>
       <c r="G63">
-        <v>4.339829190991803</v>
+        <v>3.940808800867705</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -4344,22 +4344,22 @@
         </is>
       </c>
       <c r="B64">
-        <v>1.009795274985396</v>
+        <v>1.974228046675315</v>
       </c>
       <c r="C64">
-        <v>0.7450779566104565</v>
+        <v>0.7382907525973189</v>
       </c>
       <c r="D64">
-        <v>0.01308267435159117</v>
+        <v>0.9212867113812495</v>
       </c>
       <c r="E64">
-        <v>0.9895618338814703</v>
+        <v>0.3569007571270047</v>
       </c>
       <c r="F64">
-        <v>0.2344346639755443</v>
+        <v>0.4644757978682965</v>
       </c>
       <c r="G64">
-        <v>4.349555138694007</v>
+        <v>8.391344389023685</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -4407,22 +4407,22 @@
         </is>
       </c>
       <c r="B65">
-        <v>2.96739346062667</v>
+        <v>1.784854895511504</v>
       </c>
       <c r="C65">
-        <v>0.6872238746056597</v>
+        <v>0.6518825364142082</v>
       </c>
       <c r="D65">
-        <v>1.582721417264291</v>
+        <v>0.8887139761161287</v>
       </c>
       <c r="E65">
-        <v>0.1134849745392739</v>
+        <v>0.3741568179174121</v>
       </c>
       <c r="F65">
-        <v>0.7716300152073701</v>
+        <v>0.4974157056468348</v>
       </c>
       <c r="G65">
-        <v>11.41145857034025</v>
+        <v>6.404516306715164</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         </is>
       </c>
       <c r="O65">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="66">
@@ -4659,22 +4659,22 @@
         </is>
       </c>
       <c r="B69">
-        <v>0.9757065773492185</v>
+        <v>0.9184127359829509</v>
       </c>
       <c r="C69">
-        <v>0.4565851611584548</v>
+        <v>0.4595056404748462</v>
       </c>
       <c r="D69">
-        <v>-0.05386372099602139</v>
+        <v>-0.1852172823118871</v>
       </c>
       <c r="E69">
-        <v>0.9570437411356451</v>
+        <v>0.8530586142870896</v>
       </c>
       <c r="F69">
-        <v>0.3987247907873605</v>
+        <v>0.3731693682732486</v>
       </c>
       <c r="G69">
-        <v>2.387620100577666</v>
+        <v>2.260319375941009</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -4722,22 +4722,22 @@
         </is>
       </c>
       <c r="B70">
-        <v>0.821516060842349</v>
+        <v>1.199756557213543</v>
       </c>
       <c r="C70">
-        <v>0.451047630595425</v>
+        <v>0.4347875290049268</v>
       </c>
       <c r="D70">
-        <v>-0.4358825492700816</v>
+        <v>0.4188681944060081</v>
       </c>
       <c r="E70">
-        <v>0.6629219469311924</v>
+        <v>0.6753124627395101</v>
       </c>
       <c r="F70">
-        <v>0.3393779478066131</v>
+        <v>0.5116833867107436</v>
       </c>
       <c r="G70">
-        <v>1.98860486541247</v>
+        <v>2.8130985565701</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -4785,22 +4785,22 @@
         </is>
       </c>
       <c r="B71">
-        <v>1.76464072938048</v>
+        <v>1.452015255130247</v>
       </c>
       <c r="C71">
-        <v>0.357749101124435</v>
+        <v>0.3642482710975187</v>
       </c>
       <c r="D71">
-        <v>1.587557075955036</v>
+        <v>1.023896205496644</v>
       </c>
       <c r="E71">
-        <v>0.1123865309499226</v>
+        <v>0.3058843026749437</v>
       </c>
       <c r="F71">
-        <v>0.8752653015593149</v>
+        <v>0.711086590164249</v>
       </c>
       <c r="G71">
-        <v>3.557729180216388</v>
+        <v>2.964967038183019</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         </is>
       </c>
       <c r="O71">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="72">
@@ -4974,22 +4974,22 @@
         </is>
       </c>
       <c r="B74">
-        <v>1.071123699244842</v>
+        <v>1.100389641409399</v>
       </c>
       <c r="C74">
-        <v>0.1146550022853175</v>
+        <v>0.1189490321250765</v>
       </c>
       <c r="D74">
-        <v>0.5992611072756018</v>
+        <v>0.8042464477215696</v>
       </c>
       <c r="E74">
-        <v>0.5489987790976651</v>
+        <v>0.4212546587937478</v>
       </c>
       <c r="F74">
-        <v>0.8555494443219646</v>
+        <v>0.8715592044068609</v>
       </c>
       <c r="G74">
-        <v>1.341016567421432</v>
+        <v>1.389300183852862</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         </is>
       </c>
       <c r="O74">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="75">
@@ -5037,22 +5037,22 @@
         </is>
       </c>
       <c r="B75">
-        <v>1.084209403265518</v>
+        <v>1.012143096087919</v>
       </c>
       <c r="C75">
-        <v>0.1153150295146958</v>
+        <v>0.1163148115333794</v>
       </c>
       <c r="D75">
-        <v>0.7011320306273602</v>
+        <v>0.1037697607602982</v>
       </c>
       <c r="E75">
-        <v>0.483220622596844</v>
+        <v>0.9173520643003402</v>
       </c>
       <c r="F75">
-        <v>0.8648819598878795</v>
+        <v>0.8058135576318494</v>
       </c>
       <c r="G75">
-        <v>1.359156607084</v>
+        <v>1.271303563033956</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         </is>
       </c>
       <c r="O75">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="76">
@@ -5100,22 +5100,22 @@
         </is>
       </c>
       <c r="B76">
-        <v>0.9741935846047567</v>
+        <v>1.085871891457913</v>
       </c>
       <c r="C76">
-        <v>0.1138178179394593</v>
+        <v>0.1155321401831996</v>
       </c>
       <c r="D76">
-        <v>-0.2297113351897304</v>
+        <v>0.7130764716736071</v>
       </c>
       <c r="E76">
-        <v>0.8183160862200319</v>
+        <v>0.4757984378821727</v>
       </c>
       <c r="F76">
-        <v>0.7794053148948047</v>
+        <v>0.8658396208193766</v>
       </c>
       <c r="G76">
-        <v>1.217663162090648</v>
+        <v>1.361820060327734</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="O76">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="77">
@@ -5163,22 +5163,22 @@
         </is>
       </c>
       <c r="B77">
-        <v>1.244974979651029</v>
+        <v>1.156336160808099</v>
       </c>
       <c r="C77">
-        <v>0.1044141876704039</v>
+        <v>0.1072232104384256</v>
       </c>
       <c r="D77">
-        <v>2.098521646699529</v>
+        <v>1.354711577184858</v>
       </c>
       <c r="E77">
-        <v>0.03585908974332904</v>
+        <v>0.1755094678764406</v>
       </c>
       <c r="F77">
-        <v>1.01457254487892</v>
+        <v>0.9371638867306088</v>
       </c>
       <c r="G77">
-        <v>1.52770021994046</v>
+        <v>1.426765729798946</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         </is>
       </c>
       <c r="O77">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="78">
@@ -5226,22 +5226,22 @@
         </is>
       </c>
       <c r="B78">
-        <v>1.679869201501077</v>
+        <v>2.079998502917444</v>
       </c>
       <c r="C78">
-        <v>0.8470198406501657</v>
+        <v>0.8425138123592476</v>
       </c>
       <c r="D78">
-        <v>0.6124011613903771</v>
+        <v>0.8692642936154708</v>
       </c>
       <c r="E78">
-        <v>0.5402723736027395</v>
+        <v>0.3847025882139093</v>
       </c>
       <c r="F78">
-        <v>0.3193676130355253</v>
+        <v>0.3989458623067144</v>
       </c>
       <c r="G78">
-        <v>8.836088629431446</v>
+        <v>10.84456358846159</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         </is>
       </c>
       <c r="O78">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="79">
@@ -5289,22 +5289,22 @@
         </is>
       </c>
       <c r="B79">
-        <v>1.319762689214534</v>
+        <v>0.8336401052834277</v>
       </c>
       <c r="C79">
-        <v>0.7772268020833881</v>
+        <v>0.8250588941139501</v>
       </c>
       <c r="D79">
-        <v>0.3569768036742363</v>
+        <v>-0.2205339515685388</v>
       </c>
       <c r="E79">
-        <v>0.7211091711776818</v>
+        <v>0.8254553336512732</v>
       </c>
       <c r="F79">
-        <v>0.2876863081245697</v>
+        <v>0.1654577811030573</v>
       </c>
       <c r="G79">
-        <v>6.054419368086789</v>
+        <v>4.20020032000854</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         </is>
       </c>
       <c r="O79">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="80">
@@ -5352,22 +5352,22 @@
         </is>
       </c>
       <c r="B80">
-        <v>0.9677078935354091</v>
+        <v>1.809282341398598</v>
       </c>
       <c r="C80">
-        <v>0.7812502787023407</v>
+        <v>0.8531916245386251</v>
       </c>
       <c r="D80">
-        <v>-0.04201598516714062</v>
+        <v>0.6949555681679357</v>
       </c>
       <c r="E80">
-        <v>0.9664859550490348</v>
+        <v>0.487083146958454</v>
       </c>
       <c r="F80">
-        <v>0.2092872833685519</v>
+        <v>0.339835165657137</v>
       </c>
       <c r="G80">
-        <v>4.474512508061222</v>
+        <v>9.632618756704716</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         </is>
       </c>
       <c r="O80">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="81">
@@ -5415,22 +5415,22 @@
         </is>
       </c>
       <c r="B81">
-        <v>3.081361052585483</v>
+        <v>1.829247013330386</v>
       </c>
       <c r="C81">
-        <v>0.7860887324448926</v>
+        <v>0.7799402396311605</v>
       </c>
       <c r="D81">
-        <v>1.431608612511607</v>
+        <v>0.7742957516042646</v>
       </c>
       <c r="E81">
-        <v>0.1522558634466906</v>
+        <v>0.4387559154396171</v>
       </c>
       <c r="F81">
-        <v>0.6601196287674159</v>
+        <v>0.3966304192670967</v>
       </c>
       <c r="G81">
-        <v>14.38343221836852</v>
+        <v>8.436429666592955</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="O81">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="82">
@@ -5478,22 +5478,22 @@
         </is>
       </c>
       <c r="B82">
-        <v>1.356831524309774</v>
+        <v>1.594567191655911</v>
       </c>
       <c r="C82">
-        <v>0.6992196796226373</v>
+        <v>0.6978060892199746</v>
       </c>
       <c r="D82">
-        <v>0.4364182373396269</v>
+        <v>0.6686704994816859</v>
       </c>
       <c r="E82">
-        <v>0.6625333094101278</v>
+        <v>0.5037056899062842</v>
       </c>
       <c r="F82">
-        <v>0.3446268059742261</v>
+        <v>0.4061338650537912</v>
       </c>
       <c r="G82">
-        <v>5.341986616962314</v>
+        <v>6.260607025145892</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         </is>
       </c>
       <c r="O82">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="83">
@@ -5541,22 +5541,22 @@
         </is>
       </c>
       <c r="B83">
-        <v>1.392098475169698</v>
+        <v>0.8805893742456238</v>
       </c>
       <c r="C83">
-        <v>0.6604080393996784</v>
+        <v>0.6903151442964844</v>
       </c>
       <c r="D83">
-        <v>0.500921072019534</v>
+        <v>-0.184211303022487</v>
       </c>
       <c r="E83">
-        <v>0.6164266718191365</v>
+        <v>0.8538476926893339</v>
       </c>
       <c r="F83">
-        <v>0.38153081080259</v>
+        <v>0.2276020264909755</v>
       </c>
       <c r="G83">
-        <v>5.079375268521937</v>
+        <v>3.406989199479055</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         </is>
       </c>
       <c r="O83">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="84">
@@ -5604,22 +5604,22 @@
         </is>
       </c>
       <c r="B84">
-        <v>0.8136368502582612</v>
+        <v>1.45164608779106</v>
       </c>
       <c r="C84">
-        <v>0.6596880002334563</v>
+        <v>0.7007610768273423</v>
       </c>
       <c r="D84">
-        <v>-0.3126343701204506</v>
+        <v>0.5318476693790317</v>
       </c>
       <c r="E84">
-        <v>0.7545584625610062</v>
+        <v>0.5948315038924467</v>
       </c>
       <c r="F84">
-        <v>0.2233074262365597</v>
+        <v>0.3675968980769771</v>
       </c>
       <c r="G84">
-        <v>2.964545045613003</v>
+        <v>5.732573847121563</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         </is>
       </c>
       <c r="O84">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="85">
@@ -5667,22 +5667,22 @@
         </is>
       </c>
       <c r="B85">
-        <v>3.041327652928457</v>
+        <v>1.88898981609645</v>
       </c>
       <c r="C85">
-        <v>0.644624054962457</v>
+        <v>0.6433362832645755</v>
       </c>
       <c r="D85">
-        <v>1.725492772810059</v>
+        <v>0.9886620945985748</v>
       </c>
       <c r="E85">
-        <v>0.08443870512555589</v>
+        <v>0.3228284944406485</v>
       </c>
       <c r="F85">
-        <v>0.8597223563802994</v>
+        <v>0.5353290107165233</v>
       </c>
       <c r="G85">
-        <v>10.7589081798586</v>
+        <v>6.665587804666239</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         </is>
       </c>
       <c r="O85">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="86">
@@ -5730,22 +5730,22 @@
         </is>
       </c>
       <c r="B86">
-        <v>1.002994458598352</v>
+        <v>1.034075737751041</v>
       </c>
       <c r="C86">
-        <v>0.0553227040421958</v>
+        <v>0.06091520602871808</v>
       </c>
       <c r="D86">
-        <v>0.05404623995041354</v>
+        <v>0.550076457582971</v>
       </c>
       <c r="E86">
-        <v>0.9568983238991655</v>
+        <v>0.5822669333628518</v>
       </c>
       <c r="F86">
-        <v>0.8999279959910863</v>
+        <v>0.917701055332902</v>
       </c>
       <c r="G86">
-        <v>1.11786486081156</v>
+        <v>1.165208021927641</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         </is>
       </c>
       <c r="O86">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="87">
@@ -5793,22 +5793,22 @@
         </is>
       </c>
       <c r="B87">
-        <v>1.019501931449259</v>
+        <v>0.9685826328607162</v>
       </c>
       <c r="C87">
-        <v>0.06251038195072144</v>
+        <v>0.06225596682666926</v>
       </c>
       <c r="D87">
-        <v>0.3089759642196484</v>
+        <v>-0.5127457004803062</v>
       </c>
       <c r="E87">
-        <v>0.7573398106211717</v>
+        <v>0.6081292172331588</v>
       </c>
       <c r="F87">
-        <v>0.901943055987781</v>
+        <v>0.8573226597456298</v>
       </c>
       <c r="G87">
-        <v>1.152383380889237</v>
+        <v>1.094281489022755</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         </is>
       </c>
       <c r="O87">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="88">
@@ -5856,22 +5856,22 @@
         </is>
       </c>
       <c r="B88">
-        <v>0.9537200183573628</v>
+        <v>1.018090055739617</v>
       </c>
       <c r="C88">
-        <v>0.0612615141000366</v>
+        <v>0.05724228066563038</v>
       </c>
       <c r="D88">
-        <v>-0.7734894102745442</v>
+        <v>0.3132016650217953</v>
       </c>
       <c r="E88">
-        <v>0.4392327935440365</v>
+        <v>0.7541274535189604</v>
       </c>
       <c r="F88">
-        <v>0.8458142605243377</v>
+        <v>0.9100420871881204</v>
       </c>
       <c r="G88">
-        <v>1.075391981274588</v>
+        <v>1.138966401871075</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         </is>
       </c>
       <c r="O88">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="89">
@@ -5919,22 +5919,22 @@
         </is>
       </c>
       <c r="B89">
-        <v>1.093173305909871</v>
+        <v>1.046205293896876</v>
       </c>
       <c r="C89">
-        <v>0.04805225827211865</v>
+        <v>0.05475694490266641</v>
       </c>
       <c r="D89">
-        <v>1.853914044267805</v>
+        <v>0.8249111074626967</v>
       </c>
       <c r="E89">
-        <v>0.06375145831472598</v>
+        <v>0.409422059781422</v>
       </c>
       <c r="F89">
-        <v>0.9949170231503908</v>
+        <v>0.939740009275881</v>
       </c>
       <c r="G89">
-        <v>1.201133209048808</v>
+        <v>1.164732272941377</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="O89">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="90">
@@ -5982,22 +5982,22 @@
         </is>
       </c>
       <c r="B90">
-        <v>1.707423177111129</v>
+        <v>2.272173405418178</v>
       </c>
       <c r="C90">
-        <v>0.646526900116177</v>
+        <v>0.677618445128704</v>
       </c>
       <c r="D90">
-        <v>0.8274757321181212</v>
+        <v>1.211207910076705</v>
       </c>
       <c r="E90">
-        <v>0.4079674714721034</v>
+        <v>0.2258157319260407</v>
       </c>
       <c r="F90">
-        <v>0.4808575919925231</v>
+        <v>0.6020764026902083</v>
       </c>
       <c r="G90">
-        <v>6.06269705268913</v>
+        <v>8.574944909352451</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         </is>
       </c>
       <c r="O90">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="91">
@@ -6045,22 +6045,22 @@
         </is>
       </c>
       <c r="B91">
-        <v>1.247239642383401</v>
+        <v>0.7820429243331545</v>
       </c>
       <c r="C91">
-        <v>0.6583000162034036</v>
+        <v>0.6835586522040138</v>
       </c>
       <c r="D91">
-        <v>0.3356111467774687</v>
+        <v>-0.3596555302152373</v>
       </c>
       <c r="E91">
-        <v>0.7371641171809394</v>
+        <v>0.7191047513435769</v>
       </c>
       <c r="F91">
-        <v>0.3432447602995326</v>
+        <v>0.2048256828512302</v>
       </c>
       <c r="G91">
-        <v>4.532062555522109</v>
+        <v>2.985910394565927</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         </is>
       </c>
       <c r="O91">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="92">
@@ -6108,22 +6108,22 @@
         </is>
       </c>
       <c r="B92">
-        <v>1.007465485764143</v>
+        <v>1.950819217118842</v>
       </c>
       <c r="C92">
-        <v>0.6421586636412182</v>
+        <v>0.6521565751802264</v>
       </c>
       <c r="D92">
-        <v>0.01158242871577858</v>
+        <v>1.024676314138081</v>
       </c>
       <c r="E92">
-        <v>0.9907587655742314</v>
+        <v>0.3055159426931401</v>
       </c>
       <c r="F92">
-        <v>0.2861697547540168</v>
+        <v>0.5433758616497314</v>
       </c>
       <c r="G92">
-        <v>3.546799366964664</v>
+        <v>7.00379955474243</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         </is>
       </c>
       <c r="O92">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="93">
@@ -6171,22 +6171,22 @@
         </is>
       </c>
       <c r="B93">
-        <v>2.77364856361658</v>
+        <v>1.630391242325126</v>
       </c>
       <c r="C93">
-        <v>0.5878676935791696</v>
+        <v>0.6309330414576048</v>
       </c>
       <c r="D93">
-        <v>1.73536262600194</v>
+        <v>0.7747573511986193</v>
       </c>
       <c r="E93">
-        <v>0.08267659555654176</v>
+        <v>0.438483054908176</v>
       </c>
       <c r="F93">
-        <v>0.876309550233893</v>
+        <v>0.4734135185903582</v>
       </c>
       <c r="G93">
-        <v>8.779005492293185</v>
+        <v>5.614912753158136</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         </is>
       </c>
       <c r="O93">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="94">
@@ -6234,22 +6234,22 @@
         </is>
       </c>
       <c r="B94">
-        <v>1.027407232001695</v>
+        <v>1.241277386115368</v>
       </c>
       <c r="C94">
-        <v>0.3695563028612462</v>
+        <v>0.3975780828564991</v>
       </c>
       <c r="D94">
-        <v>0.07316443515226202</v>
+        <v>0.5436441513993394</v>
       </c>
       <c r="E94">
-        <v>0.9416752671466759</v>
+        <v>0.5866863710883716</v>
       </c>
       <c r="F94">
-        <v>0.4979385188456676</v>
+        <v>0.5694423536419085</v>
       </c>
       <c r="G94">
-        <v>2.119871390581353</v>
+        <v>2.705751582100104</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         </is>
       </c>
       <c r="O94">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="95">
@@ -6297,22 +6297,22 @@
         </is>
       </c>
       <c r="B95">
-        <v>1.184597694893969</v>
+        <v>0.8385553751736146</v>
       </c>
       <c r="C95">
-        <v>0.3973253946076123</v>
+        <v>0.4047462032976045</v>
       </c>
       <c r="D95">
-        <v>0.4263589019577618</v>
+        <v>-0.4350248568344209</v>
       </c>
       <c r="E95">
-        <v>0.6698463436167447</v>
+        <v>0.6635443850571786</v>
       </c>
       <c r="F95">
-        <v>0.5437094660195674</v>
+        <v>0.3793247272974323</v>
       </c>
       <c r="G95">
-        <v>2.580921956392063</v>
+        <v>1.853755019459079</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
         </is>
       </c>
       <c r="O95">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="96">
@@ -6360,22 +6360,22 @@
         </is>
       </c>
       <c r="B96">
-        <v>0.7147635578962849</v>
+        <v>1.116129759156283</v>
       </c>
       <c r="C96">
-        <v>0.3941317088872333</v>
+        <v>0.3775095434408557</v>
       </c>
       <c r="D96">
-        <v>-0.8520082796245421</v>
+        <v>0.291031394449299</v>
       </c>
       <c r="E96">
-        <v>0.394209496677721</v>
+        <v>0.7710273089241113</v>
       </c>
       <c r="F96">
-        <v>0.3301238361615981</v>
+        <v>0.5325715734911869</v>
       </c>
       <c r="G96">
-        <v>1.547561513996441</v>
+        <v>2.339114029515279</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         </is>
       </c>
       <c r="O96">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="97">
@@ -6423,22 +6423,22 @@
         </is>
       </c>
       <c r="B97">
-        <v>1.929644326427125</v>
+        <v>1.424277064909621</v>
       </c>
       <c r="C97">
-        <v>0.317219489081495</v>
+        <v>0.3566240908811683</v>
       </c>
       <c r="D97">
-        <v>2.072179426969869</v>
+        <v>0.9917007043593963</v>
       </c>
       <c r="E97">
-        <v>0.03824871127033241</v>
+        <v>0.3213435473637036</v>
       </c>
       <c r="F97">
-        <v>1.036238080962783</v>
+        <v>0.7080036626778178</v>
       </c>
       <c r="G97">
-        <v>3.593312478009699</v>
+        <v>2.865190202484415</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -6476,7 +6476,7 @@
         </is>
       </c>
       <c r="O97">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="98">
@@ -6486,22 +6486,22 @@
         </is>
       </c>
       <c r="B98">
-        <v>0.8955700812278221</v>
+        <v>0.9125648395208273</v>
       </c>
       <c r="C98">
-        <v>0.2390182586912955</v>
+        <v>0.2375730754651679</v>
       </c>
       <c r="D98">
-        <v>-0.4614492709461675</v>
+        <v>-0.3851284025415967</v>
       </c>
       <c r="E98">
-        <v>0.644476308996106</v>
+        <v>0.7001422857935448</v>
       </c>
       <c r="F98">
-        <v>0.5605919612515909</v>
+        <v>0.5728503242295041</v>
       </c>
       <c r="G98">
-        <v>1.430712221773108</v>
+        <v>1.453738526638303</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         </is>
       </c>
       <c r="O98">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="99">
@@ -6549,22 +6549,22 @@
         </is>
       </c>
       <c r="B99">
-        <v>1.129740649775299</v>
+        <v>1.082063296258876</v>
       </c>
       <c r="C99">
-        <v>0.1873820238517532</v>
+        <v>0.2114970793611577</v>
       </c>
       <c r="D99">
-        <v>0.651012783410457</v>
+        <v>0.3729114286899174</v>
       </c>
       <c r="E99">
-        <v>0.5150382349140882</v>
+        <v>0.7092143657246914</v>
       </c>
       <c r="F99">
-        <v>0.7824901651142938</v>
+        <v>0.7148682776271185</v>
       </c>
       <c r="G99">
-        <v>1.631092622829695</v>
+        <v>1.637869540101982</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         </is>
       </c>
       <c r="O99">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="100">
@@ -6612,22 +6612,22 @@
         </is>
       </c>
       <c r="B100">
-        <v>0.9233514671764068</v>
+        <v>1.07519167630289</v>
       </c>
       <c r="C100">
-        <v>0.210110618559416</v>
+        <v>0.2483799547792394</v>
       </c>
       <c r="D100">
-        <v>-0.3795397380067695</v>
+        <v>0.2918872792591052</v>
       </c>
       <c r="E100">
-        <v>0.7042871010677163</v>
+        <v>0.7703728098661593</v>
       </c>
       <c r="F100">
-        <v>0.6116747608411227</v>
+        <v>0.6607915683445065</v>
       </c>
       <c r="G100">
-        <v>1.393841934501975</v>
+        <v>1.749473201795326</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         </is>
       </c>
       <c r="O100">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="101">
@@ -6675,22 +6675,22 @@
         </is>
       </c>
       <c r="B101">
-        <v>1.258065854151907</v>
+        <v>1.207449854742575</v>
       </c>
       <c r="C101">
-        <v>0.2079951488521448</v>
+        <v>0.2029479885699823</v>
       </c>
       <c r="D101">
-        <v>1.10375413305324</v>
+        <v>0.9288615218463711</v>
       </c>
       <c r="E101">
-        <v>0.2696998062950065</v>
+        <v>0.352960856222394</v>
       </c>
       <c r="F101">
-        <v>0.8368691979891932</v>
+        <v>0.8111841617439213</v>
       </c>
       <c r="G101">
-        <v>1.89125098305196</v>
+        <v>1.797292428125728</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         </is>
       </c>
       <c r="O101">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="102">
@@ -6738,22 +6738,22 @@
         </is>
       </c>
       <c r="B102">
-        <v>0.2148100833795509</v>
+        <v>0.2324410972872197</v>
       </c>
       <c r="C102">
-        <v>1.530281629068125</v>
+        <v>1.527925638533233</v>
       </c>
       <c r="D102">
-        <v>-1.005044395179741</v>
+        <v>-0.9549669134774857</v>
       </c>
       <c r="E102">
-        <v>0.3148754730923815</v>
+        <v>0.3395944292102273</v>
       </c>
       <c r="F102">
-        <v>0.01070228666306046</v>
+        <v>0.01163429992675574</v>
       </c>
       <c r="G102">
-        <v>4.311543259329434</v>
+        <v>4.643929075941645</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="O102">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="103">
@@ -6801,22 +6801,22 @@
         </is>
       </c>
       <c r="B103">
-        <v>1.675338755229375</v>
+        <v>0.7799548094234894</v>
       </c>
       <c r="C103">
-        <v>1.222326623302172</v>
+        <v>1.404817856995181</v>
       </c>
       <c r="D103">
-        <v>0.4221583469750774</v>
+        <v>-0.1769049961715399</v>
       </c>
       <c r="E103">
-        <v>0.6729094421909366</v>
+        <v>0.8595830141433052</v>
       </c>
       <c r="F103">
-        <v>0.1526357717813301</v>
+        <v>0.04969198123968186</v>
       </c>
       <c r="G103">
-        <v>18.38861173902633</v>
+        <v>12.24200544165556</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -6854,7 +6854,7 @@
         </is>
       </c>
       <c r="O103">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="104">
@@ -6864,22 +6864,22 @@
         </is>
       </c>
       <c r="B104">
-        <v>0.2714671545169301</v>
+        <v>0.5879288636977622</v>
       </c>
       <c r="C104">
-        <v>1.287612814386854</v>
+        <v>1.552923542547135</v>
       </c>
       <c r="D104">
-        <v>-1.012660102630043</v>
+        <v>-0.3420318540839677</v>
       </c>
       <c r="E104">
-        <v>0.3112225410496361</v>
+        <v>0.7323269202510989</v>
       </c>
       <c r="F104">
-        <v>0.02176202355646538</v>
+        <v>0.02802037001854964</v>
       </c>
       <c r="G104">
-        <v>3.386376997079602</v>
+        <v>12.33603798023055</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         </is>
       </c>
       <c r="O104">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="105">
@@ -6927,22 +6927,22 @@
         </is>
       </c>
       <c r="B105">
-        <v>2.481493622176318</v>
+        <v>1.341175466487839</v>
       </c>
       <c r="C105">
-        <v>1.390428276000607</v>
+        <v>1.356256716804162</v>
       </c>
       <c r="D105">
-        <v>0.6536551806237048</v>
+        <v>0.2164387019031717</v>
       </c>
       <c r="E105">
-        <v>0.5133339847822036</v>
+        <v>0.828645801376011</v>
       </c>
       <c r="F105">
-        <v>0.1626216896384846</v>
+        <v>0.09398050841563117</v>
       </c>
       <c r="G105">
-        <v>37.86586285378557</v>
+        <v>19.13962439907057</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         </is>
       </c>
       <c r="O105">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="106">
@@ -6990,22 +6990,22 @@
         </is>
       </c>
       <c r="B106">
-        <v>0.2566138064642954</v>
+        <v>0.2660315231981485</v>
       </c>
       <c r="C106">
-        <v>1.340752395918988</v>
+        <v>1.330852232917719</v>
       </c>
       <c r="D106">
-        <v>-1.0144923305701</v>
+        <v>-0.9949567925022502</v>
       </c>
       <c r="E106">
-        <v>0.3103478871746336</v>
+        <v>0.3197572792504023</v>
       </c>
       <c r="F106">
-        <v>0.01853657575214839</v>
+        <v>0.01959339196525166</v>
       </c>
       <c r="G106">
-        <v>3.552470885053447</v>
+        <v>3.612073471537781</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         </is>
       </c>
       <c r="O106">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="107">
@@ -7053,22 +7053,22 @@
         </is>
       </c>
       <c r="B107">
-        <v>1.68826395894861</v>
+        <v>0.9632619053030549</v>
       </c>
       <c r="C107">
-        <v>1.061265738515285</v>
+        <v>1.218028905387669</v>
       </c>
       <c r="D107">
-        <v>0.4934680718761731</v>
+        <v>-0.03072992428295063</v>
       </c>
       <c r="E107">
-        <v>0.6216818942924305</v>
+        <v>0.9754849263001303</v>
       </c>
       <c r="F107">
-        <v>0.2109061844620692</v>
+        <v>0.08850265541531294</v>
       </c>
       <c r="G107">
-        <v>13.51423241738764</v>
+        <v>10.48413173428386</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
         </is>
       </c>
       <c r="O107">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="108">
@@ -7116,22 +7116,22 @@
         </is>
       </c>
       <c r="B108">
-        <v>0.3257419070531034</v>
+        <v>0.6562671144749616</v>
       </c>
       <c r="C108">
-        <v>1.149642297615664</v>
+        <v>1.365136278929926</v>
       </c>
       <c r="D108">
-        <v>-0.9756512174741148</v>
+        <v>-0.3085313845344216</v>
       </c>
       <c r="E108">
-        <v>0.3292373342582938</v>
+        <v>0.7576780228290454</v>
       </c>
       <c r="F108">
-        <v>0.03422128685905052</v>
+        <v>0.04519334999789579</v>
       </c>
       <c r="G108">
-        <v>3.100637052242535</v>
+        <v>9.529865025747041</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
         </is>
       </c>
       <c r="O108">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="109">
@@ -7179,22 +7179,22 @@
         </is>
       </c>
       <c r="B109">
-        <v>2.487925192737749</v>
+        <v>1.650176134890761</v>
       </c>
       <c r="C109">
-        <v>1.166001953824114</v>
+        <v>1.156129037322684</v>
       </c>
       <c r="D109">
-        <v>0.7816874613357636</v>
+        <v>0.4332405937955225</v>
       </c>
       <c r="E109">
-        <v>0.4343982723104132</v>
+        <v>0.6648399908697898</v>
       </c>
       <c r="F109">
-        <v>0.2531247754579867</v>
+        <v>0.1711715097731414</v>
       </c>
       <c r="G109">
-        <v>24.45344100931967</v>
+        <v>15.90849598611352</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         </is>
       </c>
       <c r="O109">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="110">
@@ -7242,22 +7242,22 @@
         </is>
       </c>
       <c r="B110">
-        <v>0.9383435235739125</v>
+        <v>0.9599641891037262</v>
       </c>
       <c r="C110">
-        <v>0.07605313125987941</v>
+        <v>0.08690764855546507</v>
       </c>
       <c r="D110">
-        <v>-0.836772479245998</v>
+        <v>-0.4701461713914077</v>
       </c>
       <c r="E110">
-        <v>0.4027204695875405</v>
+        <v>0.6382505889070093</v>
       </c>
       <c r="F110">
-        <v>0.8083981633763477</v>
+        <v>0.8096160472942145</v>
       </c>
       <c r="G110">
-        <v>1.089176853836068</v>
+        <v>1.138232434301898</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         </is>
       </c>
       <c r="O110">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="111">
@@ -7305,22 +7305,22 @@
         </is>
       </c>
       <c r="B111">
-        <v>1.074229757979531</v>
+        <v>1.014316623060957</v>
       </c>
       <c r="C111">
-        <v>0.08900942784024814</v>
+        <v>0.09046875351758744</v>
       </c>
       <c r="D111">
-        <v>0.8044529922294842</v>
+        <v>0.1571272667669456</v>
       </c>
       <c r="E111">
-        <v>0.4211354072190628</v>
+        <v>0.8751445487165117</v>
       </c>
       <c r="F111">
-        <v>0.9022610645134788</v>
+        <v>0.8495059016817483</v>
       </c>
       <c r="G111">
-        <v>1.278975252634901</v>
+        <v>1.211101900270517</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         </is>
       </c>
       <c r="O111">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="112">
@@ -7368,22 +7368,22 @@
         </is>
       </c>
       <c r="B112">
-        <v>0.9176209300746437</v>
+        <v>1.000508468680547</v>
       </c>
       <c r="C112">
-        <v>0.08571238156213717</v>
+        <v>0.08217960759682449</v>
       </c>
       <c r="D112">
-        <v>-1.003016160277707</v>
+        <v>0.006185712843069856</v>
       </c>
       <c r="E112">
-        <v>0.3158530641458503</v>
+        <v>0.9950645466992186</v>
       </c>
       <c r="F112">
-        <v>0.775719661724438</v>
+        <v>0.8516660988719158</v>
       </c>
       <c r="G112">
-        <v>1.085479990850317</v>
+        <v>1.175363440234854</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="O112">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="113">
@@ -7431,22 +7431,22 @@
         </is>
       </c>
       <c r="B113">
-        <v>1.108891921144869</v>
+        <v>1.060154660058434</v>
       </c>
       <c r="C113">
-        <v>0.06148753227041522</v>
+        <v>0.0731718004263771</v>
       </c>
       <c r="D113">
-        <v>1.681011477712653</v>
+        <v>0.7983239835003257</v>
       </c>
       <c r="E113">
-        <v>0.09276068517919811</v>
+        <v>0.4246825036493721</v>
       </c>
       <c r="F113">
-        <v>0.982994158608182</v>
+        <v>0.9185129362483863</v>
       </c>
       <c r="G113">
-        <v>1.250914140244132</v>
+        <v>1.223638621611835</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
         </is>
       </c>
       <c r="O113">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="114">
@@ -7494,22 +7494,22 @@
         </is>
       </c>
       <c r="B114">
-        <v>0.5945459092353559</v>
+        <v>0.7606089797665178</v>
       </c>
       <c r="C114">
-        <v>0.8982048730512426</v>
+        <v>0.9586803593571707</v>
       </c>
       <c r="D114">
-        <v>-0.5788850162817418</v>
+        <v>-0.2854297313231141</v>
       </c>
       <c r="E114">
-        <v>0.5626667611120584</v>
+        <v>0.7753149321821452</v>
       </c>
       <c r="F114">
-        <v>0.1022426320875063</v>
+        <v>0.1161799665396671</v>
       </c>
       <c r="G114">
-        <v>3.457313558652904</v>
+        <v>4.979567797550859</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="O114">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="115">
@@ -7557,22 +7557,22 @@
         </is>
       </c>
       <c r="B115">
-        <v>2.661003779967249</v>
+        <v>1.46149501917703</v>
       </c>
       <c r="C115">
-        <v>0.9327683148505614</v>
+        <v>0.940894041257944</v>
       </c>
       <c r="D115">
-        <v>1.049245988439943</v>
+        <v>0.4032971630204397</v>
       </c>
       <c r="E115">
-        <v>0.2940649175686662</v>
+        <v>0.6867296285227749</v>
       </c>
       <c r="F115">
-        <v>0.4276334436065448</v>
+        <v>0.2311569096289358</v>
       </c>
       <c r="G115">
-        <v>16.55843625625079</v>
+        <v>9.240336767384646</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         </is>
       </c>
       <c r="O115">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="116">
@@ -7620,22 +7620,22 @@
         </is>
       </c>
       <c r="B116">
-        <v>0.5211698409715366</v>
+        <v>1.63261185885281</v>
       </c>
       <c r="C116">
-        <v>0.9358984092555701</v>
+        <v>0.907227188878277</v>
       </c>
       <c r="D116">
-        <v>-0.696314144311878</v>
+        <v>0.540306888727873</v>
       </c>
       <c r="E116">
-        <v>0.4862321171475787</v>
+        <v>0.588985408454737</v>
       </c>
       <c r="F116">
-        <v>0.08324173158679694</v>
+        <v>0.27583524878023</v>
       </c>
       <c r="G116">
-        <v>3.263002798723356</v>
+        <v>9.663092347528375</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         </is>
       </c>
       <c r="O116">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="117">
@@ -7683,22 +7683,22 @@
         </is>
       </c>
       <c r="B117">
-        <v>4.396449608679161</v>
+        <v>2.261944295074632</v>
       </c>
       <c r="C117">
-        <v>0.7916836296556551</v>
+        <v>0.8432237671134089</v>
       </c>
       <c r="D117">
-        <v>1.870440732398546</v>
+        <v>0.9679811964753701</v>
       </c>
       <c r="E117">
-        <v>0.0614226400549473</v>
+        <v>0.3330537606843477</v>
       </c>
       <c r="F117">
-        <v>0.931579176902692</v>
+        <v>0.4332399863750511</v>
       </c>
       <c r="G117">
-        <v>20.7483911629705</v>
+        <v>11.8096024257361</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         </is>
       </c>
       <c r="O117">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="118">
@@ -7746,22 +7746,22 @@
         </is>
       </c>
       <c r="B118">
-        <v>0.5706664229402558</v>
+        <v>0.635660288536304</v>
       </c>
       <c r="C118">
-        <v>0.519253968914673</v>
+        <v>0.5784702690700153</v>
       </c>
       <c r="D118">
-        <v>-1.080300723000352</v>
+        <v>-0.7832571872608598</v>
       </c>
       <c r="E118">
-        <v>0.2800082878671947</v>
+        <v>0.4334760987479141</v>
       </c>
       <c r="F118">
-        <v>0.2062493271776653</v>
+        <v>0.20456451236291</v>
       </c>
       <c r="G118">
-        <v>1.578963532767794</v>
+        <v>1.975239975667054</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         </is>
       </c>
       <c r="O118">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="119">
@@ -7809,22 +7809,22 @@
         </is>
       </c>
       <c r="B119">
-        <v>1.963263250380229</v>
+        <v>1.315478172269966</v>
       </c>
       <c r="C119">
-        <v>0.5772456156423492</v>
+        <v>0.5886513260708227</v>
       </c>
       <c r="D119">
-        <v>1.168667191531924</v>
+        <v>0.4658109418789189</v>
       </c>
       <c r="E119">
-        <v>0.2425377453225439</v>
+        <v>0.6413508323050833</v>
       </c>
       <c r="F119">
-        <v>0.6333243388351527</v>
+        <v>0.4149757600749741</v>
       </c>
       <c r="G119">
-        <v>6.085985258963497</v>
+        <v>4.170081696834734</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
         </is>
       </c>
       <c r="O119">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="120">
@@ -7872,22 +7872,22 @@
         </is>
       </c>
       <c r="B120">
-        <v>0.4404415020306647</v>
+        <v>0.8656397953074373</v>
       </c>
       <c r="C120">
-        <v>0.5745785913417967</v>
+        <v>0.550059850595526</v>
       </c>
       <c r="D120">
-        <v>-1.427093967305554</v>
+        <v>-0.2623103604896366</v>
       </c>
       <c r="E120">
-        <v>0.1535528111468218</v>
+        <v>0.7930821750973881</v>
       </c>
       <c r="F120">
-        <v>0.1428255980962407</v>
+        <v>0.2945272076618371</v>
       </c>
       <c r="G120">
-        <v>1.358220930258677</v>
+        <v>2.544186872135262</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="O120">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="121">
@@ -7935,22 +7935,22 @@
         </is>
       </c>
       <c r="B121">
-        <v>2.430046268680056</v>
+        <v>1.783680182630505</v>
       </c>
       <c r="C121">
-        <v>0.4132495648914484</v>
+        <v>0.4810943760334653</v>
       </c>
       <c r="D121">
-        <v>2.148605523670662</v>
+        <v>1.202838314245557</v>
       </c>
       <c r="E121">
-        <v>0.03166568345669724</v>
+        <v>0.2290388949398316</v>
       </c>
       <c r="F121">
-        <v>1.081075127039602</v>
+        <v>0.6947182565071436</v>
       </c>
       <c r="G121">
-        <v>5.462270586223143</v>
+        <v>4.579575913125693</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         </is>
       </c>
       <c r="O121">
-        <v>7575</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="122">
@@ -7998,22 +7998,22 @@
         </is>
       </c>
       <c r="B122">
-        <v>1.106904496514614</v>
+        <v>1.045836440693224</v>
       </c>
       <c r="C122">
-        <v>0.1095083330700749</v>
+        <v>0.1079532112611024</v>
       </c>
       <c r="D122">
-        <v>0.9274853777137788</v>
+        <v>0.4151519574323133</v>
       </c>
       <c r="E122">
-        <v>0.3536745802848689</v>
+        <v>0.6780306659030488</v>
       </c>
       <c r="F122">
-        <v>0.8930925972393098</v>
+        <v>0.8463964440754355</v>
       </c>
       <c r="G122">
-        <v>1.371904288750879</v>
+        <v>1.29227133258654</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         </is>
       </c>
       <c r="O122">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="123">
@@ -8061,22 +8061,22 @@
         </is>
       </c>
       <c r="B123">
-        <v>0.9204073031375558</v>
+        <v>1.002129372642348</v>
       </c>
       <c r="C123">
-        <v>0.06453680375599172</v>
+        <v>0.05952149707279075</v>
       </c>
       <c r="D123">
-        <v>-1.285142450234822</v>
+        <v>0.03573681520551596</v>
       </c>
       <c r="E123">
-        <v>0.1987425098026864</v>
+        <v>0.9714922150012473</v>
       </c>
       <c r="F123">
-        <v>0.8110473862639057</v>
+        <v>0.8917826144944268</v>
       </c>
       <c r="G123">
-        <v>1.044513080266922</v>
+        <v>1.126130138881311</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         </is>
       </c>
       <c r="O123">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="124">
@@ -8124,22 +8124,22 @@
         </is>
       </c>
       <c r="B124">
-        <v>1.246258016876783</v>
+        <v>1.186833633483453</v>
       </c>
       <c r="C124">
-        <v>0.104473236615191</v>
+        <v>0.1021958001488839</v>
       </c>
       <c r="D124">
-        <v>2.107194935329844</v>
+        <v>1.676085988096699</v>
       </c>
       <c r="E124">
-        <v>0.03510068577262806</v>
+        <v>0.0937213509192195</v>
       </c>
       <c r="F124">
-        <v>1.015500601095587</v>
+        <v>0.9714056439274298</v>
       </c>
       <c r="G124">
-        <v>1.529451625094073</v>
+        <v>1.450036946329255</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="O124">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="125">
@@ -8187,22 +8187,22 @@
         </is>
       </c>
       <c r="B125">
-        <v>1.287604959755147</v>
+        <v>0.8395261378638704</v>
       </c>
       <c r="C125">
-        <v>0.7709470868834749</v>
+        <v>0.8164101694987022</v>
       </c>
       <c r="D125">
-        <v>0.3278874473665817</v>
+        <v>-0.2142521914190056</v>
       </c>
       <c r="E125">
-        <v>0.7429967650942351</v>
+        <v>0.8303503980254523</v>
       </c>
       <c r="F125">
-        <v>0.284152375314755</v>
+        <v>0.1694746032465335</v>
       </c>
       <c r="G125">
-        <v>5.834639005039363</v>
+        <v>4.158759617400332</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         </is>
       </c>
       <c r="O125">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="126">
@@ -8250,22 +8250,22 @@
         </is>
       </c>
       <c r="B126">
-        <v>0.6357449952874862</v>
+        <v>0.9295436416840248</v>
       </c>
       <c r="C126">
-        <v>0.385369589399777</v>
+        <v>0.3800142126630263</v>
       </c>
       <c r="D126">
-        <v>-1.175385290665032</v>
+        <v>-0.1922599700310899</v>
       </c>
       <c r="E126">
-        <v>0.2398406056187503</v>
+        <v>0.847538572692932</v>
       </c>
       <c r="F126">
-        <v>0.2987141261406027</v>
+        <v>0.4413682616511362</v>
       </c>
       <c r="G126">
-        <v>1.353038452700576</v>
+        <v>1.957665416545418</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         </is>
       </c>
       <c r="O126">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="127">
@@ -8313,22 +8313,22 @@
         </is>
       </c>
       <c r="B127">
-        <v>2.625272387474166</v>
+        <v>1.791109464075199</v>
       </c>
       <c r="C127">
-        <v>0.7389228062865406</v>
+        <v>0.7787574623117841</v>
       </c>
       <c r="D127">
-        <v>1.306204990704732</v>
+        <v>0.7484168927905595</v>
       </c>
       <c r="E127">
-        <v>0.1914828561009159</v>
+        <v>0.4542087362983566</v>
       </c>
       <c r="F127">
-        <v>0.6168820561246562</v>
+        <v>0.3892625066578253</v>
       </c>
       <c r="G127">
-        <v>11.17240328196805</v>
+        <v>8.241413075828921</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="O127">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="128">
@@ -8376,22 +8376,22 @@
         </is>
       </c>
       <c r="B128">
-        <v>1.407537101320814</v>
+        <v>0.9182045864183465</v>
       </c>
       <c r="C128">
-        <v>0.6574800387706572</v>
+        <v>0.6820943690443403</v>
       </c>
       <c r="D128">
-        <v>0.5199267205952921</v>
+        <v>-0.1251073986857147</v>
       </c>
       <c r="E128">
-        <v>0.6031146507147664</v>
+        <v>0.9004385260159893</v>
       </c>
       <c r="F128">
-        <v>0.3879822235001911</v>
+        <v>0.2411791044407273</v>
       </c>
       <c r="G128">
-        <v>5.106318206338196</v>
+        <v>3.495740912027844</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         </is>
       </c>
       <c r="O128">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="129">
@@ -8439,22 +8439,22 @@
         </is>
       </c>
       <c r="B129">
-        <v>0.6376622123640168</v>
+        <v>0.9651847770467399</v>
       </c>
       <c r="C129">
-        <v>0.3616956612315629</v>
+        <v>0.3500414230422657</v>
       </c>
       <c r="D129">
-        <v>-1.243992206092609</v>
+        <v>-0.1012329251206569</v>
       </c>
       <c r="E129">
-        <v>0.213502431424883</v>
+        <v>0.9193655604973686</v>
       </c>
       <c r="F129">
-        <v>0.3138446838311286</v>
+        <v>0.4860205852836408</v>
       </c>
       <c r="G129">
-        <v>1.295587014931756</v>
+        <v>1.916753491622367</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         </is>
       </c>
       <c r="O129">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="130">
@@ -8502,22 +8502,22 @@
         </is>
       </c>
       <c r="B130">
-        <v>2.831956517848074</v>
+        <v>1.924329547209804</v>
       </c>
       <c r="C130">
-        <v>0.6236634108674449</v>
+        <v>0.6429347025748673</v>
       </c>
       <c r="D130">
-        <v>1.669117994910954</v>
+        <v>1.018109019918279</v>
       </c>
       <c r="E130">
-        <v>0.09509399770245386</v>
+        <v>0.3086261492591078</v>
       </c>
       <c r="F130">
-        <v>0.8341099907472919</v>
+        <v>0.5457734906793977</v>
       </c>
       <c r="G130">
-        <v>9.615012178186442</v>
+        <v>6.784946996335443</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         </is>
       </c>
       <c r="O130">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="131">
@@ -8565,22 +8565,22 @@
         </is>
       </c>
       <c r="B131">
-        <v>1.022021535694819</v>
+        <v>0.9922941489925048</v>
       </c>
       <c r="C131">
-        <v>0.04529161748227543</v>
+        <v>0.04334942853509419</v>
       </c>
       <c r="D131">
-        <v>0.4809402904733217</v>
+        <v>-0.1784497454888847</v>
       </c>
       <c r="E131">
-        <v>0.6305589362937265</v>
+        <v>0.8583697849373213</v>
       </c>
       <c r="F131">
-        <v>0.9352070078776775</v>
+        <v>0.9114677988188623</v>
       </c>
       <c r="G131">
-        <v>1.116894987554046</v>
+        <v>1.080287948077516</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         </is>
       </c>
       <c r="O131">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="132">
@@ -8628,22 +8628,22 @@
         </is>
       </c>
       <c r="B132">
-        <v>0.9510266150584804</v>
+        <v>0.9921563352961851</v>
       </c>
       <c r="C132">
-        <v>0.03772020979818635</v>
+        <v>0.03363103124146598</v>
       </c>
       <c r="D132">
-        <v>-1.331202310521097</v>
+        <v>-0.2341464938430928</v>
       </c>
       <c r="E132">
-        <v>0.1831224513667185</v>
+        <v>0.8148712521106348</v>
       </c>
       <c r="F132">
-        <v>0.8832530998706416</v>
+        <v>0.9288665514175644</v>
       </c>
       <c r="G132">
-        <v>1.024000507535217</v>
+        <v>1.059758468174013</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         </is>
       </c>
       <c r="O132">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="133">
@@ -8691,22 +8691,22 @@
         </is>
       </c>
       <c r="B133">
-        <v>1.094754894810899</v>
+        <v>1.068931213649768</v>
       </c>
       <c r="C133">
-        <v>0.03965811989617381</v>
+        <v>0.03790630778685952</v>
       </c>
       <c r="D133">
-        <v>2.282773315884399</v>
+        <v>1.758527469937382</v>
       </c>
       <c r="E133">
-        <v>0.02244372455658943</v>
+        <v>0.07865780177639668</v>
       </c>
       <c r="F133">
-        <v>1.012884307723176</v>
+        <v>0.9923933634885578</v>
       </c>
       <c r="G133">
-        <v>1.183243012626447</v>
+        <v>1.151372007868068</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         </is>
       </c>
       <c r="O133">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="134">
@@ -8754,22 +8754,22 @@
         </is>
       </c>
       <c r="B134">
-        <v>1.474859957888546</v>
+        <v>1.064417687938345</v>
       </c>
       <c r="C134">
-        <v>0.6202850718363602</v>
+        <v>0.6211328247035348</v>
       </c>
       <c r="D134">
-        <v>0.6264265563083988</v>
+        <v>0.1005064863027456</v>
       </c>
       <c r="E134">
-        <v>0.5310351954836537</v>
+        <v>0.9199422335896463</v>
       </c>
       <c r="F134">
-        <v>0.4372835845454422</v>
+        <v>0.3150669609520473</v>
       </c>
       <c r="G134">
-        <v>4.974373546732018</v>
+        <v>3.596013402904694</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         </is>
       </c>
       <c r="O134">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="135">
@@ -8817,22 +8817,22 @@
         </is>
       </c>
       <c r="B135">
-        <v>0.6465668465763444</v>
+        <v>0.991193116407141</v>
       </c>
       <c r="C135">
-        <v>0.3640438755340965</v>
+        <v>0.3421106525314735</v>
       </c>
       <c r="D135">
-        <v>-1.197873986569307</v>
+        <v>-0.02585681951771251</v>
       </c>
       <c r="E135">
-        <v>0.23096607828795</v>
+        <v>0.9793715415532914</v>
       </c>
       <c r="F135">
-        <v>0.3167661186993253</v>
+        <v>0.5069360329578452</v>
       </c>
       <c r="G135">
-        <v>1.319739272647686</v>
+        <v>1.938042928770459</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         </is>
       </c>
       <c r="O135">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="136">
@@ -8880,22 +8880,22 @@
         </is>
       </c>
       <c r="B136">
-        <v>2.859640526018854</v>
+        <v>2.146999136000933</v>
       </c>
       <c r="C136">
-        <v>0.5856621186180693</v>
+        <v>0.5864560970985174</v>
       </c>
       <c r="D136">
-        <v>1.794030881164236</v>
+        <v>1.302861578650548</v>
       </c>
       <c r="E136">
-        <v>0.07280823996429511</v>
+        <v>0.1926220230939729</v>
       </c>
       <c r="F136">
-        <v>0.9073919957513066</v>
+        <v>0.6802045533128364</v>
       </c>
       <c r="G136">
-        <v>9.012140261694187</v>
+        <v>6.776792756735228</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="O136">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="137">
@@ -8943,22 +8943,22 @@
         </is>
       </c>
       <c r="B137">
-        <v>1.204457679369339</v>
+        <v>0.9492402536208544</v>
       </c>
       <c r="C137">
-        <v>0.3367175471175082</v>
+        <v>0.3308033123938627</v>
       </c>
       <c r="D137">
-        <v>0.5524790989174835</v>
+        <v>-0.1574752894652544</v>
       </c>
       <c r="E137">
-        <v>0.5806201505506637</v>
+        <v>0.8748702810542698</v>
       </c>
       <c r="F137">
-        <v>0.6225540305834806</v>
+        <v>0.4963589494263365</v>
       </c>
       <c r="G137">
-        <v>2.330268908599156</v>
+        <v>1.815333560794208</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         </is>
       </c>
       <c r="O137">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="138">
@@ -9006,22 +9006,22 @@
         </is>
       </c>
       <c r="B138">
-        <v>0.6979219149234757</v>
+        <v>0.9458436907202885</v>
       </c>
       <c r="C138">
-        <v>0.2505256319196029</v>
+        <v>0.2282788334836169</v>
       </c>
       <c r="D138">
-        <v>-1.435573875052462</v>
+        <v>-0.2439032762241052</v>
       </c>
       <c r="E138">
-        <v>0.151123633062126</v>
+        <v>0.8073057317384007</v>
       </c>
       <c r="F138">
-        <v>0.42712897252244</v>
+        <v>0.6046555950403075</v>
       </c>
       <c r="G138">
-        <v>1.140393255118888</v>
+        <v>1.479553475752986</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         </is>
       </c>
       <c r="O138">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="139">
@@ -9069,22 +9069,22 @@
         </is>
       </c>
       <c r="B139">
-        <v>1.945856128524685</v>
+        <v>1.59137666487392</v>
       </c>
       <c r="C139">
-        <v>0.2966580135639514</v>
+        <v>0.2913551210434457</v>
       </c>
       <c r="D139">
-        <v>2.244004944057512</v>
+        <v>1.594615762788123</v>
       </c>
       <c r="E139">
-        <v>0.02483208324018666</v>
+        <v>0.1107981855217757</v>
       </c>
       <c r="F139">
-        <v>1.087915007005535</v>
+        <v>0.89902352636377</v>
       </c>
       <c r="G139">
-        <v>3.480378566832118</v>
+        <v>2.816922600177348</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         </is>
       </c>
       <c r="O139">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="140">
@@ -9132,22 +9132,22 @@
         </is>
       </c>
       <c r="B140">
-        <v>1.153255064627826</v>
+        <v>1.104495167603147</v>
       </c>
       <c r="C140">
-        <v>0.1816459326633156</v>
+        <v>0.2047266476664967</v>
       </c>
       <c r="D140">
-        <v>0.7849800596612122</v>
+        <v>0.4854686471534632</v>
       </c>
       <c r="E140">
-        <v>0.4324652599390306</v>
+        <v>0.6273439476577107</v>
       </c>
       <c r="F140">
-        <v>0.807807855855882</v>
+        <v>0.7394353035376051</v>
       </c>
       <c r="G140">
-        <v>1.646427717245438</v>
+        <v>1.649785409788272</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="O140">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="141">
@@ -9195,22 +9195,22 @@
         </is>
       </c>
       <c r="B141">
-        <v>0.9921200020368239</v>
+        <v>1.160310769177786</v>
       </c>
       <c r="C141">
-        <v>0.1429521336755539</v>
+        <v>0.1522299647888807</v>
       </c>
       <c r="D141">
-        <v>-0.0553416658774042</v>
+        <v>0.9767319719747453</v>
       </c>
       <c r="E141">
-        <v>0.9558662684394743</v>
+        <v>0.3287018624097153</v>
       </c>
       <c r="F141">
-        <v>0.7496924353684022</v>
+        <v>0.8609857074345002</v>
       </c>
       <c r="G141">
-        <v>1.312941216964337</v>
+        <v>1.563697363898887</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         </is>
       </c>
       <c r="O141">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="142">
@@ -9258,22 +9258,22 @@
         </is>
       </c>
       <c r="B142">
-        <v>1.329394798133889</v>
+        <v>1.239174957132274</v>
       </c>
       <c r="C142">
-        <v>0.169366555506433</v>
+        <v>0.1906148852184255</v>
       </c>
       <c r="D142">
-        <v>1.681109938284773</v>
+        <v>1.12502127402861</v>
       </c>
       <c r="E142">
-        <v>0.09274156236120971</v>
+        <v>0.2605800194418479</v>
       </c>
       <c r="F142">
-        <v>0.9538693664967519</v>
+        <v>0.8528662793281575</v>
       </c>
       <c r="G142">
-        <v>1.852759498710099</v>
+        <v>1.800463462564613</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         </is>
       </c>
       <c r="O142">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="143">
@@ -9321,22 +9321,22 @@
         </is>
       </c>
       <c r="B143">
-        <v>2.541489192707516</v>
+        <v>1.293288661957293</v>
       </c>
       <c r="C143">
-        <v>1.149747141525707</v>
+        <v>1.297592104659038</v>
       </c>
       <c r="D143">
-        <v>0.8112655138500128</v>
+        <v>0.1982042921834822</v>
       </c>
       <c r="E143">
-        <v>0.4172132099565681</v>
+        <v>0.8428852294299892</v>
       </c>
       <c r="F143">
-        <v>0.266944960267855</v>
+        <v>0.1016677162720833</v>
       </c>
       <c r="G143">
-        <v>24.19662581442974</v>
+        <v>16.45158979150353</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         </is>
       </c>
       <c r="O143">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="144">
@@ -9384,22 +9384,22 @@
         </is>
       </c>
       <c r="B144">
-        <v>0.6987016088748201</v>
+        <v>1.945733299913712</v>
       </c>
       <c r="C144">
-        <v>0.8923684634821821</v>
+        <v>0.9321472790118115</v>
       </c>
       <c r="D144">
-        <v>-0.4017751920079552</v>
+        <v>0.7140920098733243</v>
       </c>
       <c r="E144">
-        <v>0.6878494811490412</v>
+        <v>0.475170286376215</v>
       </c>
       <c r="F144">
-        <v>0.1215363893619211</v>
+        <v>0.3130675893987634</v>
       </c>
       <c r="G144">
-        <v>4.016771773518035</v>
+        <v>12.09284577066493</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="O144">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="145">
@@ -9447,22 +9447,22 @@
         </is>
       </c>
       <c r="B145">
-        <v>5.788294265590035</v>
+        <v>2.306886770887076</v>
       </c>
       <c r="C145">
-        <v>1.09240283793389</v>
+        <v>1.220880495237211</v>
       </c>
       <c r="D145">
-        <v>1.607316996202488</v>
+        <v>0.6846688931266562</v>
       </c>
       <c r="E145">
-        <v>0.1079848477776566</v>
+        <v>0.4935528826219484</v>
       </c>
       <c r="F145">
-        <v>0.6802924016236506</v>
+        <v>0.2107710295412085</v>
       </c>
       <c r="G145">
-        <v>49.24992609809812</v>
+        <v>25.24885220363426</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         </is>
       </c>
       <c r="O145">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="146">
@@ -9510,22 +9510,22 @@
         </is>
       </c>
       <c r="B146">
-        <v>2.351082607891439</v>
+        <v>1.430889024010653</v>
       </c>
       <c r="C146">
-        <v>1.00949513474096</v>
+        <v>1.151013687247878</v>
       </c>
       <c r="D146">
-        <v>0.84683509297166</v>
+        <v>0.3112873028195814</v>
       </c>
       <c r="E146">
-        <v>0.397087044868018</v>
+        <v>0.7555822190115532</v>
       </c>
       <c r="F146">
-        <v>0.3250753750284717</v>
+        <v>0.1499206047763032</v>
       </c>
       <c r="G146">
-        <v>17.00402384722459</v>
+        <v>13.65685125196203</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         </is>
       </c>
       <c r="O146">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="147">
@@ -9573,22 +9573,22 @@
         </is>
       </c>
       <c r="B147">
-        <v>0.7566616242497542</v>
+        <v>1.921866568388445</v>
       </c>
       <c r="C147">
-        <v>0.8071895658279388</v>
+        <v>0.8506552006328411</v>
       </c>
       <c r="D147">
-        <v>-0.3454444073469966</v>
+        <v>0.7679925830549307</v>
       </c>
       <c r="E147">
-        <v>0.7297602972260813</v>
+        <v>0.442491591332839</v>
       </c>
       <c r="F147">
-        <v>0.1555323393477873</v>
+        <v>0.3627807318634522</v>
       </c>
       <c r="G147">
-        <v>3.681143201556439</v>
+        <v>10.18127695954759</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -9626,7 +9626,7 @@
         </is>
       </c>
       <c r="O147">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="148">
@@ -9636,22 +9636,22 @@
         </is>
       </c>
       <c r="B148">
-        <v>5.056929804537327</v>
+        <v>2.573430234091158</v>
       </c>
       <c r="C148">
-        <v>0.9229397610849853</v>
+        <v>1.056510029465352</v>
       </c>
       <c r="D148">
-        <v>1.756083776524424</v>
+        <v>0.8946812657073033</v>
       </c>
       <c r="E148">
-        <v>0.0790741048377283</v>
+        <v>0.3709574961511512</v>
       </c>
       <c r="F148">
-        <v>0.8284745585140584</v>
+        <v>0.3244960625976991</v>
       </c>
       <c r="G148">
-        <v>30.86701792494934</v>
+        <v>20.40870116179163</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         </is>
       </c>
       <c r="O148">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="149">
@@ -9699,22 +9699,22 @@
         </is>
       </c>
       <c r="B149">
-        <v>1.028174230959475</v>
+        <v>0.9869228117122452</v>
       </c>
       <c r="C149">
-        <v>0.07262017415837894</v>
+        <v>0.06993037377407182</v>
       </c>
       <c r="D149">
-        <v>0.3826021950937977</v>
+        <v>-0.1882364822113305</v>
       </c>
       <c r="E149">
-        <v>0.7020147424381444</v>
+        <v>0.8506912749573476</v>
       </c>
       <c r="F149">
-        <v>0.8917688757674861</v>
+        <v>0.8605148022323117</v>
       </c>
       <c r="G149">
-        <v>1.185444208623333</v>
+        <v>1.131899920549013</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         </is>
       </c>
       <c r="O149">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="150">
@@ -9762,22 +9762,22 @@
         </is>
       </c>
       <c r="B150">
-        <v>0.9480718597298927</v>
+        <v>1.021676575092685</v>
       </c>
       <c r="C150">
-        <v>0.07569436683752856</v>
+        <v>0.06906735850146775</v>
       </c>
       <c r="D150">
-        <v>-0.7044774984578903</v>
+        <v>0.3104936895602702</v>
       </c>
       <c r="E150">
-        <v>0.4811354582276778</v>
+        <v>0.7561855575344076</v>
       </c>
       <c r="F150">
-        <v>0.8173538156061047</v>
+        <v>0.8923252737517118</v>
       </c>
       <c r="G150">
-        <v>1.09969542449027</v>
+        <v>1.169778616383291</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         </is>
       </c>
       <c r="O150">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="151">
@@ -9825,22 +9825,22 @@
         </is>
       </c>
       <c r="B151">
-        <v>1.083139855634578</v>
+        <v>1.036113490610858</v>
       </c>
       <c r="C151">
-        <v>0.05490773164409164</v>
+        <v>0.05544408860025987</v>
       </c>
       <c r="D151">
-        <v>1.454514592633493</v>
+        <v>0.6398641524243019</v>
       </c>
       <c r="E151">
-        <v>0.145803690707199</v>
+        <v>0.5222609210659009</v>
       </c>
       <c r="F151">
-        <v>0.9726284989999956</v>
+        <v>0.9294226128356883</v>
       </c>
       <c r="G151">
-        <v>1.206207661065152</v>
+        <v>1.155051696182053</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         </is>
       </c>
       <c r="O151">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="152">
@@ -9888,22 +9888,22 @@
         </is>
       </c>
       <c r="B152">
-        <v>2.312116649336662</v>
+        <v>1.337588394987577</v>
       </c>
       <c r="C152">
-        <v>0.9045609446675524</v>
+        <v>0.8915411058069684</v>
       </c>
       <c r="D152">
-        <v>0.9265969400334445</v>
+        <v>0.326253366692787</v>
       </c>
       <c r="E152">
-        <v>0.3541358442596078</v>
+        <v>0.7442326674918756</v>
       </c>
       <c r="F152">
-        <v>0.3926865885151569</v>
+        <v>0.2330458250303698</v>
       </c>
       <c r="G152">
-        <v>13.61361339167165</v>
+        <v>7.67721418812067</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -9941,7 +9941,7 @@
         </is>
       </c>
       <c r="O152">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="153">
@@ -9951,22 +9951,22 @@
         </is>
       </c>
       <c r="B153">
-        <v>0.6884107555384825</v>
+        <v>1.892238397628838</v>
       </c>
       <c r="C153">
-        <v>0.7990199160431224</v>
+        <v>0.7455799366868049</v>
       </c>
       <c r="D153">
-        <v>-0.4672844610048951</v>
+        <v>0.855388449025493</v>
       </c>
       <c r="E153">
-        <v>0.6402963723965628</v>
+        <v>0.3923361361410533</v>
       </c>
       <c r="F153">
-        <v>0.1437873439309588</v>
+        <v>0.4388711759490416</v>
       </c>
       <c r="G153">
-        <v>3.295904600398056</v>
+        <v>8.158581264121798</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -10004,7 +10004,7 @@
         </is>
       </c>
       <c r="O153">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="154">
@@ -10014,22 +10014,22 @@
         </is>
       </c>
       <c r="B154">
-        <v>4.301715742870573</v>
+        <v>2.075075458858537</v>
       </c>
       <c r="C154">
-        <v>0.7889762861157132</v>
+        <v>0.7924805114655064</v>
       </c>
       <c r="D154">
-        <v>1.849249437228492</v>
+        <v>0.9211551680765545</v>
       </c>
       <c r="E154">
-        <v>0.06442180314454962</v>
+        <v>0.3569694208319979</v>
       </c>
       <c r="F154">
-        <v>0.9163552588207274</v>
+        <v>0.4390088344024509</v>
       </c>
       <c r="G154">
-        <v>20.19386930378356</v>
+        <v>9.80831778890718</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
         </is>
       </c>
       <c r="O154">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="155">
@@ -10077,22 +10077,22 @@
         </is>
       </c>
       <c r="B155">
-        <v>1.471242344202007</v>
+        <v>1.0291997772324</v>
       </c>
       <c r="C155">
-        <v>0.5145145802699096</v>
+        <v>0.5047627104827682</v>
       </c>
       <c r="D155">
-        <v>0.7504299990395755</v>
+        <v>0.05702003016538881</v>
       </c>
       <c r="E155">
-        <v>0.4529957689040595</v>
+        <v>0.9545292393334565</v>
       </c>
       <c r="F155">
-        <v>0.5366963123079965</v>
+        <v>0.3826880363128019</v>
       </c>
       <c r="G155">
-        <v>4.033107710512521</v>
+        <v>2.767926041433418</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         </is>
       </c>
       <c r="O155">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="156">
@@ -10140,22 +10140,22 @@
         </is>
       </c>
       <c r="B156">
-        <v>0.5779125881635365</v>
+        <v>1.08193226753109</v>
       </c>
       <c r="C156">
-        <v>0.510438045239695</v>
+        <v>0.4692533012015191</v>
       </c>
       <c r="D156">
-        <v>-1.074239387935687</v>
+        <v>0.1678167824049804</v>
       </c>
       <c r="E156">
-        <v>0.2827154031330281</v>
+        <v>0.8667274192911339</v>
       </c>
       <c r="F156">
-        <v>0.2125085962900536</v>
+        <v>0.4312915399123862</v>
       </c>
       <c r="G156">
-        <v>1.571620938580871</v>
+        <v>2.7141210137411</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         </is>
       </c>
       <c r="O156">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="157">
@@ -10203,22 +10203,22 @@
         </is>
       </c>
       <c r="B157">
-        <v>2.114574855623903</v>
+        <v>1.441234777846233</v>
       </c>
       <c r="C157">
-        <v>0.3909736982929257</v>
+        <v>0.4018767904039903</v>
       </c>
       <c r="D157">
-        <v>1.915355896502729</v>
+        <v>0.9094833030940217</v>
       </c>
       <c r="E157">
-        <v>0.05544713160308786</v>
+        <v>0.3630950674349654</v>
       </c>
       <c r="F157">
-        <v>0.9827106176002268</v>
+        <v>0.6556266359114094</v>
       </c>
       <c r="G157">
-        <v>4.550095155129235</v>
+        <v>3.168202100248647</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -10256,7 +10256,7 @@
         </is>
       </c>
       <c r="O157">
-        <v>7579</v>
+        <v>7547</v>
       </c>
     </row>
   </sheetData>
